--- a/Cost model - FE support.xlsx
+++ b/Cost model - FE support.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/fskna_dtu_dk/Documents/Papers DTU Energy/Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{F300E3EB-C205-438A-9B75-6A2B8044D168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7AD96CD-6C37-4CD1-9054-CD540BF2FA39}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{F300E3EB-C205-438A-9B75-6A2B8044D168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BCB3249-DDF0-49D1-8592-38B580ADD7A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6B800C1E-3020-450D-98CF-85AAE588E4EC}"/>
+    <workbookView xWindow="3150" yWindow="3660" windowWidth="28800" windowHeight="15345" xr2:uid="{6B800C1E-3020-450D-98CF-85AAE588E4EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Manufacturing results" sheetId="8" r:id="rId1"/>
@@ -1218,7 +1218,7 @@
     <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
     <numFmt numFmtId="171" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="172" formatCode="0.0%"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -1503,7 +1503,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1570,9 +1570,9 @@
     <xf numFmtId="171" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1588,12 +1588,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2011,15 +2006,6 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _k_r_._-;\-* #,##0.00\ _k_r_._-;_-* &quot;-&quot;??\ _k_r_._-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -2113,6 +2099,15 @@
           <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _k_r_._-;\-* #,##0.00\ _k_r_._-;_-* &quot;-&quot;??\ _k_r_._-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8586,10 +8581,10 @@
     <tableColumn id="1" xr3:uid="{8715D058-A2E3-4359-BB36-D0DE8001209A}" name="Table for max cycle time"/>
     <tableColumn id="2" xr3:uid="{E45E0319-C5EC-42DF-A587-08DF7FABF148}" name="Shifts/day"/>
     <tableColumn id="3" xr3:uid="{2A1AD14E-2FD5-422A-8B8E-FA31F8BC61F8}" name="Hours/shift"/>
-    <tableColumn id="5" xr3:uid="{FCBB932C-0601-430A-A554-D602E803DC96}" name="Hours/year" dataDxfId="23">
+    <tableColumn id="5" xr3:uid="{FCBB932C-0601-430A-A554-D602E803DC96}" name="Hours/year" dataDxfId="32">
       <calculatedColumnFormula>$B$12*Max_cycle_table[[#This Row],[Shifts/day]]*Max_cycle_table[[#This Row],[Hours/shift]]*$B$11</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C2B59697-F58A-4CA9-8E58-7CC2433EE403}" name="Takt time" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{C2B59697-F58A-4CA9-8E58-7CC2433EE403}" name="Takt time" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8600,7 +8595,7 @@
   <autoFilter ref="A18:B22" xr:uid="{7EA27FFB-8A9A-443F-8721-AF6153862C3F}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{459A5AC5-6FB0-42AC-8A8D-7CFE35FE7CC8}" name="Scaling factors"/>
-    <tableColumn id="2" xr3:uid="{53752033-101B-4735-8F6D-7055D47504EE}" name="Value" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{53752033-101B-4735-8F6D-7055D47504EE}" name="Value" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8611,32 +8606,32 @@
   <autoFilter ref="A2:M10" xr:uid="{DA5E36E3-84B8-48B5-9F00-CE9B0028B83A}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{EB16A435-BF7C-498A-93CF-3E27E6C2FFB0}" name="Layer"/>
-    <tableColumn id="2" xr3:uid="{6BA6BBE5-C520-4626-8E5B-085D5F583AA8}" name="Material" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{6BA6BBE5-C520-4626-8E5B-085D5F583AA8}" name="Material" dataDxfId="29"/>
     <tableColumn id="3" xr3:uid="{416AF623-AAB5-45D8-93E0-B17B5F1652BE}" name="Mat. Price">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B3,Tabel2[Material],Tabel2[Cost],"Not found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{DEA13BDD-35F1-41BB-B3D1-63E23D541A9E}" name="Thickness" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{F6505740-4A1B-45A7-8A48-D5AD74A96C3B}" name="Porosity" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{36D0C33C-0CCA-4C0D-A081-6B536C01F122}" name="Fraction in layer" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{1151C9D4-C7F7-4D06-98A9-AD78539EEF80}" name="Volume%" dataDxfId="28">
+    <tableColumn id="4" xr3:uid="{DEA13BDD-35F1-41BB-B3D1-63E23D541A9E}" name="Thickness" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{F6505740-4A1B-45A7-8A48-D5AD74A96C3B}" name="Porosity" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{36D0C33C-0CCA-4C0D-A081-6B536C01F122}" name="Fraction in layer" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{1151C9D4-C7F7-4D06-98A9-AD78539EEF80}" name="Volume%" dataDxfId="25">
       <calculatedColumnFormula>F3*(1-E3)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{992E6FD0-0DD2-4271-8484-8DC1C1FA00EE}" name="Mat. Density">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B3,Tabel2[Material],Tabel2[Density],"Not found")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{50FCCA25-0CBE-41B8-8523-05A374905A67}" name="Mass" dataDxfId="27">
+    <tableColumn id="9" xr3:uid="{50FCCA25-0CBE-41B8-8523-05A374905A67}" name="Mass" dataDxfId="24">
       <calculatedColumnFormula>H3*G3*D3/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{25724C97-30B8-4B45-BD4B-86FACE7FA220}" name="Cost per area" dataDxfId="26">
+    <tableColumn id="10" xr3:uid="{25724C97-30B8-4B45-BD4B-86FACE7FA220}" name="Cost per area" dataDxfId="23">
       <calculatedColumnFormula>I3*C3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{7C7C18FE-20F8-49B1-BC47-C56D46FDF412}" name="Area">
       <calculatedColumnFormula>'Cross-layer'!$B$25</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EE4AB578-24A7-4F0A-A767-0B1D70F57AC5}" name="Cost per unit" dataDxfId="25">
+    <tableColumn id="12" xr3:uid="{EE4AB578-24A7-4F0A-A767-0B1D70F57AC5}" name="Cost per unit" dataDxfId="22">
       <calculatedColumnFormula>K3/100/100*J3/(1-'Cross-layer'!$B$19)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{48056564-8DEF-4249-8C24-9D1FFF158EB2}" name="Mass per unit" dataDxfId="24">
+    <tableColumn id="13" xr3:uid="{48056564-8DEF-4249-8C24-9D1FFF158EB2}" name="Mass per unit" dataDxfId="21">
       <calculatedColumnFormula>K3/100/100*I3*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11561,13 +11556,12 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="84"/>
+      <c r="B12" s="18"/>
       <c r="I12" s="61" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="86"/>
       <c r="E13" t="s">
         <v>361</v>
       </c>
@@ -11590,7 +11584,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="84"/>
+      <c r="B14" s="18"/>
       <c r="E14" t="s">
         <v>365</v>
       </c>
@@ -11613,7 +11607,6 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="86"/>
       <c r="E15" t="s">
         <v>369</v>
       </c>
@@ -11636,7 +11629,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="87"/>
+      <c r="B16" s="43"/>
       <c r="E16" t="s">
         <v>370</v>
       </c>
@@ -11658,8 +11651,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="86"/>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
         <v>372</v>
       </c>
@@ -11681,7 +11673,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
       <c r="I18" t="s">
         <v>367</v>
       </c>
@@ -11693,7 +11685,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
       <c r="I19" t="s">
         <v>373</v>
       </c>
@@ -11705,47 +11697,46 @@
         <v>374</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
       <c r="J20" s="15"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
       <c r="I22" s="61"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E23" s="61"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F24" s="83"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C25" s="1"/>
-      <c r="F25" s="83"/>
+      <c r="F25" s="15"/>
       <c r="J25" s="58"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F26" s="83"/>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F26" s="15"/>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
       <c r="E27" s="15"/>
-      <c r="F27" s="84"/>
+      <c r="F27" s="18"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F28" s="83"/>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F28" s="15"/>
       <c r="G28" s="43"/>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F29" s="85"/>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F29" s="8"/>
       <c r="G29" s="43"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F30" s="86"/>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
       <c r="J30" s="15"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
       <c r="I32" s="61"/>
     </row>
     <row r="33" spans="10:10" x14ac:dyDescent="0.25">
@@ -16367,7 +16358,7 @@
         <v>90</v>
       </c>
       <c r="C5">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
